--- a/backend/data/financials_by_company/1918.HK.xlsx
+++ b/backend/data/financials_by_company/1918.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,591 +664,662 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-2065033000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-2172344000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-7788303000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-8260132000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-25695200000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2981520000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>71127085000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-9960647000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-12942167000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-9888722000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>11306711000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1417989000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-19028272000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-25695200000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>76924863000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-10936048000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>8563962000</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>4625219000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4625219000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-8.27</v>
+      </c>
       <c r="V2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-25695200000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-25695200000</v>
-      </c>
-      <c r="Y2" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>6890928000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>-25695200000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1708827000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-27404027000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-27404027000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3155149000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-24248878000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>536252000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-6011989000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-3647879000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3327283000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>5860756000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-9888722000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>11306711000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1417989000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-2905670000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5797778000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5797778000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2145136000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3652642000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2892108000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>71127085000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>74019193000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>74019193000</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>3050546250</v>
+        <v>-421431250.713728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.045095</v>
       </c>
       <c r="D3" t="n">
-        <v>-9583296000</v>
+        <v>-13304763000</v>
       </c>
       <c r="E3" t="n">
-        <v>12981237000</v>
+        <v>-8873322000</v>
       </c>
       <c r="F3" t="n">
-        <v>12202185000</v>
+        <v>-9345489000</v>
       </c>
       <c r="G3" t="n">
-        <v>-7968963000</v>
+        <v>-27669007000</v>
       </c>
       <c r="H3" t="n">
-        <v>3584039000</v>
+        <v>3189150000</v>
       </c>
       <c r="I3" t="n">
-        <v>156733635000</v>
+        <v>97570939000</v>
       </c>
       <c r="J3" t="n">
-        <v>3397941000</v>
+        <v>-22178085000</v>
       </c>
       <c r="K3" t="n">
-        <v>-186098000</v>
+        <v>-25367235000</v>
       </c>
       <c r="L3" t="n">
-        <v>-3185366000</v>
+        <v>-2325541000</v>
       </c>
       <c r="M3" t="n">
-        <v>4947822000</v>
+        <v>5936368000</v>
       </c>
       <c r="N3" t="n">
-        <v>1762456000</v>
+        <v>3610827000</v>
       </c>
       <c r="O3" t="n">
-        <v>-16341549750</v>
+        <v>-18272782250.71373</v>
       </c>
       <c r="P3" t="n">
-        <v>-7968963000</v>
+        <v>-27669007000</v>
       </c>
       <c r="Q3" t="n">
-        <v>167099708000</v>
+        <v>112814092000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1933981000</v>
+        <v>-22032772000</v>
       </c>
       <c r="S3" t="n">
-        <v>5575222000</v>
+        <v>5357699000</v>
       </c>
       <c r="T3" t="n">
-        <v>5575222000</v>
+        <v>5357699000</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.43</v>
+        <v>-5.16</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.43</v>
+        <v>-5.16</v>
       </c>
       <c r="W3" t="n">
-        <v>-7968963000</v>
+        <v>-27669007000</v>
       </c>
       <c r="X3" t="n">
-        <v>-7968963000</v>
+        <v>-27669007000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-7968963000</v>
+        <v>-27669007000</v>
       </c>
       <c r="AA3" t="n">
-        <v>2442527000</v>
+        <v>2222972000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-10411490000</v>
+        <v>-29891979000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-10411490000</v>
+        <v>-29891979000</v>
       </c>
       <c r="AD3" t="n">
-        <v>5277570000</v>
+        <v>-1411624000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-5133920000</v>
+        <v>-31303603000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1156219000</v>
+        <v>1128902000</v>
       </c>
       <c r="AG3" t="n">
-        <v>12305385000</v>
+        <v>-9513473000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-27212026000</v>
+        <v>9041306000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2524972000</v>
+        <v>2470295000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11602617000</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>-3185366000</v>
+        <v>-2325541000</v>
       </c>
       <c r="AM3" t="n">
-        <v>4947822000</v>
+        <v>5936368000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1762456000</v>
+        <v>3610827000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-12868816000</v>
+        <v>-16062328000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10366073000</v>
+        <v>15243153000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10366073000</v>
+        <v>12772858000</v>
       </c>
       <c r="AR3" t="n">
-        <v>4871869000</v>
+        <v>5790188000</v>
       </c>
       <c r="AS3" t="n">
-        <v>5494204000</v>
+        <v>6982670000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-2502743000</v>
+        <v>-819175000</v>
       </c>
       <c r="AU3" t="n">
-        <v>156733635000</v>
+        <v>97570939000</v>
       </c>
       <c r="AV3" t="n">
-        <v>154230892000</v>
+        <v>96751764000</v>
       </c>
       <c r="AW3" t="n">
-        <v>154230892000</v>
+        <v>96751764000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2470295000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-532828258.562313</v>
+        <v>3681789250</v>
       </c>
       <c r="C4" t="n">
-        <v>0.045095</v>
+        <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-10834468000</v>
+        <v>-12108268000</v>
       </c>
       <c r="E4" t="n">
-        <v>-11343617000</v>
+        <v>15506209000</v>
       </c>
       <c r="F4" t="n">
-        <v>-11815784000</v>
+        <v>14727157000</v>
       </c>
       <c r="G4" t="n">
-        <v>-27669007000</v>
+        <v>-7968963000</v>
       </c>
       <c r="H4" t="n">
-        <v>3189150000</v>
+        <v>3584039000</v>
       </c>
       <c r="I4" t="n">
-        <v>97570939000</v>
+        <v>156733635000</v>
       </c>
       <c r="J4" t="n">
-        <v>-22178085000</v>
+        <v>3397941000</v>
       </c>
       <c r="K4" t="n">
-        <v>-25367235000</v>
+        <v>-186098000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2325541000</v>
+        <v>-3185366000</v>
       </c>
       <c r="M4" t="n">
-        <v>5936368000</v>
+        <v>4947822000</v>
       </c>
       <c r="N4" t="n">
-        <v>3610827000</v>
+        <v>1762456000</v>
       </c>
       <c r="O4" t="n">
-        <v>-15913884258.56231</v>
+        <v>-18235278750</v>
       </c>
       <c r="P4" t="n">
-        <v>-27669007000</v>
+        <v>-7968963000</v>
       </c>
       <c r="Q4" t="n">
-        <v>110343797000</v>
+        <v>169624680000</v>
       </c>
       <c r="R4" t="n">
-        <v>-22032772000</v>
+        <v>-1933981000</v>
       </c>
       <c r="S4" t="n">
-        <v>5357699000</v>
+        <v>5575222000</v>
       </c>
       <c r="T4" t="n">
-        <v>5357699000</v>
+        <v>5575222000</v>
       </c>
       <c r="U4" t="n">
-        <v>-5.16</v>
+        <v>-1.43</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.16</v>
+        <v>-1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>-27669007000</v>
+        <v>-7968963000</v>
       </c>
       <c r="X4" t="n">
-        <v>-27669007000</v>
+        <v>-7968963000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-27669007000</v>
+        <v>-7968963000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2222972000</v>
+        <v>2442527000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-29891979000</v>
+        <v>-10411490000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-29891979000</v>
+        <v>-10411490000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1411624000</v>
+        <v>5277570000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-31303603000</v>
+        <v>-5133920000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1128902000</v>
+        <v>1156219000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-11983768000</v>
+        <v>14830357000</v>
       </c>
       <c r="AH4" t="n">
-        <v>9041306000</v>
+        <v>-27212026000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2470295000</v>
+        <v>2524972000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>11602617000</v>
       </c>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>-2325541000</v>
+        <v>-3185366000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5936368000</v>
+        <v>4947822000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3610827000</v>
+        <v>1762456000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-13592033000</v>
+        <v>-15393788000</v>
       </c>
       <c r="AP4" t="n">
-        <v>12772858000</v>
+        <v>12891045000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12772858000</v>
+        <v>10366073000</v>
       </c>
       <c r="AR4" t="n">
-        <v>5790188000</v>
+        <v>4871869000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6982670000</v>
+        <v>5494204000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-819175000</v>
+        <v>-2502743000</v>
       </c>
       <c r="AU4" t="n">
-        <v>97570939000</v>
+        <v>156733635000</v>
       </c>
       <c r="AV4" t="n">
-        <v>96751764000</v>
+        <v>154230892000</v>
       </c>
       <c r="AW4" t="n">
-        <v>96751764000</v>
+        <v>154230892000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2524972000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1240631376.789826</v>
+        <v>-1233212250</v>
       </c>
       <c r="C5" t="n">
-        <v>0.038321</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>-10602002000</v>
+        <v>-5499627000</v>
       </c>
       <c r="E5" t="n">
-        <v>-27189675000</v>
+        <v>-4461020000</v>
       </c>
       <c r="F5" t="n">
-        <v>-32374564000</v>
+        <v>-4932849000</v>
       </c>
       <c r="G5" t="n">
-        <v>-38264659000</v>
+        <v>-25695200000</v>
       </c>
       <c r="H5" t="n">
-        <v>3781902000</v>
+        <v>2981520000</v>
       </c>
       <c r="I5" t="n">
-        <v>200179597000</v>
+        <v>71127085000</v>
       </c>
       <c r="J5" t="n">
-        <v>-37791677000</v>
+        <v>-9960647000</v>
       </c>
       <c r="K5" t="n">
-        <v>-41573579000</v>
+        <v>-12942167000</v>
       </c>
       <c r="L5" t="n">
-        <v>3116579000</v>
+        <v>-9888722000</v>
       </c>
       <c r="M5" t="n">
-        <v>2100002000</v>
+        <v>11306711000</v>
       </c>
       <c r="N5" t="n">
-        <v>5216581000</v>
+        <v>1417989000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1945837376.789826</v>
+        <v>-21523734250</v>
       </c>
       <c r="P5" t="n">
-        <v>-38264659000</v>
+        <v>-25695200000</v>
       </c>
       <c r="Q5" t="n">
-        <v>217373940000</v>
+        <v>80252146000</v>
       </c>
       <c r="R5" t="n">
-        <v>-46098722000</v>
+        <v>-10936048000</v>
       </c>
       <c r="S5" t="n">
-        <v>4625219000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4625219000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-8.27</v>
-      </c>
+        <v>8563962000</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-8.27</v>
+        <v>-3</v>
       </c>
       <c r="W5" t="n">
-        <v>-38264659000</v>
+        <v>-25695200000</v>
       </c>
       <c r="X5" t="n">
-        <v>-38264659000</v>
+        <v>-25695200000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-38264659000</v>
+        <v>-25695200000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3735299000</v>
+        <v>1708827000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-41999958000</v>
+        <v>-27404027000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-41999958000</v>
+        <v>-27404027000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1673623000</v>
+        <v>3155149000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-43673581000</v>
+        <v>-24248878000</v>
       </c>
       <c r="AF5" t="n">
-        <v>888139000</v>
+        <v>536252000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-23473446000</v>
+        <v>-2684706000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4184423000</v>
+        <v>-3647879000</v>
       </c>
       <c r="AI5" t="n">
-        <v>6890928000</v>
+        <v>3327283000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7213206000</v>
-      </c>
-      <c r="AK5" t="n">
+        <v>5860756000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>-9888722000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>11306711000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1417989000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-6232953000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9125061000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5797778000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2145136000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3652642000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2892108000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>71127085000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>74019193000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>74019193000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3327283000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2761701750</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-9128101000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11632674000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>11046807000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-12329083000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3398612000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>45754387000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2504573000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-894039000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-12429672000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12804633000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>374961000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-20028321250</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-12329083000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>54307592000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-740672000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>-12329083000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-12329083000</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="AL5" t="n">
-        <v>3116579000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>2100002000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5216581000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-18987206000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>17194343000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>17194343000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>8766324000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8428019000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>-1792863000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>200179597000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>198386734000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>198386734000</v>
+      <c r="Z6" t="n">
+        <v>-12329083000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1380000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-13709083000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-13709083000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10411000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-13698672000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>987356000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11566138000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-19071731000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>6919726000</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>-12429672000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12804633000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>374961000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-9191078000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>8553205000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>5777487000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2150375000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3627112000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-637873000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>45754387000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>45116514000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>45116514000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>2775718000</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ5"/>
+  <dimension ref="A1:BZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1654,906 +1725,992 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>76325000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>9229924579</v>
-      </c>
-      <c r="D2" t="n">
-        <v>9306249579</v>
-      </c>
-      <c r="E2" t="n">
-        <v>251937015000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>260112738000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>25461125000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>300188792000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-53519986000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>25461125000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>445054000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>40521108000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>114102945000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>55146368000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>14625260000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40521108000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2631439000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-6920988000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>17547152000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>817490000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>817490000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>827736783000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>84749731000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>50124000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>10773159000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>73926448000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>344611000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>73581837000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>742987052000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="n">
-        <v>186186290000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>100443000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>186085847000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>7909066000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>388253364000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>178265822000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>82833553000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>127153989000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>882883151000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>193416085000</v>
-      </c>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>32972177000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>10068514000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10068514000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>62848123000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>47334307000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>15513816000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>19237181000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>15059983000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13380957000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1679026000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>53183092000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-33498942000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>86682034000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8432856000</v>
-      </c>
+        <v>3466015000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>79049000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>964236000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>77284942000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>689467066000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>4026070000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>12014562000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>24279467000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>516348360000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>541455000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>515806905000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>119764346000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>4645881000</v>
-      </c>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="n">
-        <v>8373380000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>642711000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>7730669000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>7730669000</v>
-      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="n">
+        <v>-230150000</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>3355269000</v>
+      </c>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>76325000</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>8319685376</v>
+        <v>5448884000</v>
       </c>
       <c r="D3" t="n">
-        <v>8396010376</v>
+        <v>5448884000</v>
       </c>
       <c r="E3" t="n">
-        <v>270777199000</v>
+        <v>286818089000</v>
       </c>
       <c r="F3" t="n">
-        <v>278405192000</v>
+        <v>299065875000</v>
       </c>
       <c r="G3" t="n">
-        <v>45894996000</v>
+        <v>39899059000</v>
       </c>
       <c r="H3" t="n">
-        <v>340262490000</v>
+        <v>356887679000</v>
       </c>
       <c r="I3" t="n">
-        <v>-20742120000</v>
+        <v>-96069023000</v>
       </c>
       <c r="J3" t="n">
-        <v>45894996000</v>
+        <v>39899059000</v>
       </c>
       <c r="K3" t="n">
-        <v>571619000</v>
+        <v>646658000</v>
       </c>
       <c r="L3" t="n">
-        <v>62428917000</v>
+        <v>58468462000</v>
       </c>
       <c r="M3" t="n">
-        <v>159062779000</v>
+        <v>103411479000</v>
       </c>
       <c r="N3" t="n">
-        <v>83785865000</v>
+        <v>86402837000</v>
       </c>
       <c r="O3" t="n">
-        <v>21356948000</v>
+        <v>27934375000</v>
       </c>
       <c r="P3" t="n">
-        <v>62428917000</v>
+        <v>58468462000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2620834000</v>
+        <v>2582367000</v>
       </c>
       <c r="R3" t="n">
-        <v>18801056000</v>
+        <v>27648059000</v>
       </c>
       <c r="S3" t="n">
-        <v>15077556000</v>
+        <v>7481851000</v>
       </c>
       <c r="T3" t="n">
-        <v>734205000</v>
+        <v>466030000</v>
       </c>
       <c r="U3" t="n">
-        <v>734205000</v>
+        <v>466030000</v>
       </c>
       <c r="V3" t="n">
-        <v>894068338000</v>
+        <v>1003764634000</v>
       </c>
       <c r="W3" t="n">
-        <v>114822303000</v>
+        <v>68486362000</v>
       </c>
       <c r="X3" t="n">
-        <v>2108145000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>55624000</v>
+        <v>67950000</v>
       </c>
       <c r="Z3" t="n">
-        <v>15594359000</v>
+        <v>22959345000</v>
       </c>
       <c r="AA3" t="n">
-        <v>97064175000</v>
+        <v>45459067000</v>
       </c>
       <c r="AB3" t="n">
-        <v>430313000</v>
+        <v>516050000</v>
       </c>
       <c r="AC3" t="n">
-        <v>96633862000</v>
+        <v>44943017000</v>
       </c>
       <c r="AD3" t="n">
-        <v>779246035000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
+        <v>935278272000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>510443251000</v>
+      </c>
       <c r="AF3" t="n">
-        <v>181341017000</v>
+        <v>253606808000</v>
       </c>
       <c r="AG3" t="n">
-        <v>141306000</v>
+        <v>130608000</v>
       </c>
       <c r="AH3" t="n">
-        <v>181199711000</v>
+        <v>253476200000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3489783000</v>
+        <v>1192075000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>399605291000</v>
+        <v>361633465000</v>
       </c>
       <c r="AK3" t="n">
-        <v>182022524000</v>
+        <v>169654808000</v>
       </c>
       <c r="AL3" t="n">
-        <v>82267228000</v>
+        <v>69682463000</v>
       </c>
       <c r="AM3" t="n">
-        <v>135315539000</v>
+        <v>122296194000</v>
       </c>
       <c r="AN3" t="n">
-        <v>977854203000</v>
+        <v>1090167471000</v>
       </c>
       <c r="AO3" t="n">
-        <v>219350288000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>50000000</v>
-      </c>
+        <v>250958222000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>490999000</v>
+        <v>2227644000</v>
       </c>
       <c r="AR3" t="n">
-        <v>33482587000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>33401631000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
       <c r="AT3" t="n">
-        <v>11397419000</v>
+        <v>13006130000</v>
       </c>
       <c r="AU3" t="n">
-        <v>11397419000</v>
+        <v>13006130000</v>
       </c>
       <c r="AV3" t="n">
-        <v>69251089000</v>
+        <v>75702996000</v>
       </c>
       <c r="AW3" t="n">
-        <v>53400856000</v>
+        <v>58327840000</v>
       </c>
       <c r="AX3" t="n">
-        <v>15850233000</v>
+        <v>17375156000</v>
       </c>
       <c r="AY3" t="n">
-        <v>22098863000</v>
+        <v>27048652000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>16533921000</v>
+        <v>18569403000</v>
       </c>
       <c r="BA3" t="n">
-        <v>14383298000</v>
+        <v>15644954000</v>
       </c>
       <c r="BB3" t="n">
-        <v>2150623000</v>
+        <v>2924449000</v>
       </c>
       <c r="BC3" t="n">
-        <v>65994652000</v>
+        <v>80940595000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-28164606000</v>
+        <v>-16467543000</v>
       </c>
       <c r="BE3" t="n">
-        <v>94159258000</v>
+        <v>97408138000</v>
       </c>
       <c r="BF3" t="n">
-        <v>10967852000</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>12547176000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>95358854000</v>
+      </c>
       <c r="BH3" t="n">
-        <v>1034637000</v>
+        <v>1134916000</v>
       </c>
       <c r="BI3" t="n">
-        <v>82156769000</v>
+        <v>83726046000</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>758503915000</v>
+        <v>839209249000</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>4812288000</v>
+        <v>6298764000</v>
       </c>
       <c r="BN3" t="n">
-        <v>17566748000</v>
+        <v>25940546000</v>
       </c>
       <c r="BO3" t="n">
-        <v>28079234000</v>
+        <v>29368583000</v>
       </c>
       <c r="BP3" t="n">
-        <v>577148901000</v>
+        <v>642026686000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>567532000</v>
+        <v>990898000</v>
       </c>
       <c r="BR3" t="n">
-        <v>576581369000</v>
+        <v>641035788000</v>
       </c>
       <c r="BS3" t="n">
-        <v>119032542000</v>
+        <v>118870904000</v>
       </c>
       <c r="BT3" t="n">
-        <v>4179618000</v>
-      </c>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
+        <v>3992793000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>-326640000</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>3992793000</v>
+      </c>
       <c r="BW3" t="n">
-        <v>7684584000</v>
+        <v>12710973000</v>
       </c>
       <c r="BX3" t="n">
-        <v>628210000</v>
+        <v>1109845000</v>
       </c>
       <c r="BY3" t="n">
-        <v>7056374000</v>
+        <v>11601128000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>7056374000</v>
+        <v>11601128000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>76325000</v>
+      </c>
       <c r="C4" t="n">
-        <v>5448884000</v>
+        <v>8319685376</v>
       </c>
       <c r="D4" t="n">
-        <v>5448884000</v>
+        <v>8396010376</v>
       </c>
       <c r="E4" t="n">
-        <v>286818089000</v>
+        <v>270777199000</v>
       </c>
       <c r="F4" t="n">
-        <v>299065875000</v>
+        <v>278405192000</v>
       </c>
       <c r="G4" t="n">
-        <v>39899059000</v>
+        <v>45894996000</v>
       </c>
       <c r="H4" t="n">
-        <v>356887679000</v>
+        <v>340262490000</v>
       </c>
       <c r="I4" t="n">
-        <v>-96069023000</v>
+        <v>-20742120000</v>
       </c>
       <c r="J4" t="n">
-        <v>39899059000</v>
+        <v>45894996000</v>
       </c>
       <c r="K4" t="n">
-        <v>646658000</v>
+        <v>571619000</v>
       </c>
       <c r="L4" t="n">
-        <v>58468462000</v>
+        <v>62428917000</v>
       </c>
       <c r="M4" t="n">
-        <v>103411479000</v>
+        <v>159062779000</v>
       </c>
       <c r="N4" t="n">
-        <v>86402837000</v>
+        <v>83785865000</v>
       </c>
       <c r="O4" t="n">
-        <v>27934375000</v>
+        <v>21356948000</v>
       </c>
       <c r="P4" t="n">
-        <v>58468462000</v>
+        <v>62428917000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2582367000</v>
+        <v>2620834000</v>
       </c>
       <c r="R4" t="n">
-        <v>27648059000</v>
+        <v>18801056000</v>
       </c>
       <c r="S4" t="n">
-        <v>7481851000</v>
+        <v>15077556000</v>
       </c>
       <c r="T4" t="n">
-        <v>466030000</v>
+        <v>734205000</v>
       </c>
       <c r="U4" t="n">
-        <v>466030000</v>
+        <v>734205000</v>
       </c>
       <c r="V4" t="n">
-        <v>1003764634000</v>
+        <v>894068338000</v>
       </c>
       <c r="W4" t="n">
-        <v>68486362000</v>
+        <v>114822303000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2108145000</v>
       </c>
       <c r="Y4" t="n">
-        <v>67950000</v>
+        <v>55624000</v>
       </c>
       <c r="Z4" t="n">
-        <v>22959345000</v>
+        <v>15594359000</v>
       </c>
       <c r="AA4" t="n">
-        <v>45459067000</v>
+        <v>97064175000</v>
       </c>
       <c r="AB4" t="n">
-        <v>516050000</v>
+        <v>430313000</v>
       </c>
       <c r="AC4" t="n">
-        <v>44943017000</v>
+        <v>96633862000</v>
       </c>
       <c r="AD4" t="n">
-        <v>935278272000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>510443251000</v>
-      </c>
+        <v>779246035000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="n">
-        <v>253606808000</v>
+        <v>181341017000</v>
       </c>
       <c r="AG4" t="n">
-        <v>130608000</v>
+        <v>141306000</v>
       </c>
       <c r="AH4" t="n">
-        <v>253476200000</v>
+        <v>181199711000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1192075000</v>
+        <v>3489783000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>361633465000</v>
+        <v>399605291000</v>
       </c>
       <c r="AK4" t="n">
-        <v>169654808000</v>
+        <v>182022524000</v>
       </c>
       <c r="AL4" t="n">
-        <v>69682463000</v>
+        <v>82267228000</v>
       </c>
       <c r="AM4" t="n">
-        <v>122296194000</v>
+        <v>135315539000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1090167471000</v>
+        <v>977854203000</v>
       </c>
       <c r="AO4" t="n">
-        <v>250958222000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>219350288000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>50000000</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>2227644000</v>
+        <v>490999000</v>
       </c>
       <c r="AR4" t="n">
-        <v>33401631000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
+        <v>33482587000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>13006130000</v>
+        <v>11397419000</v>
       </c>
       <c r="AU4" t="n">
-        <v>13006130000</v>
+        <v>11397419000</v>
       </c>
       <c r="AV4" t="n">
-        <v>75702996000</v>
+        <v>69251089000</v>
       </c>
       <c r="AW4" t="n">
-        <v>58327840000</v>
+        <v>53400856000</v>
       </c>
       <c r="AX4" t="n">
-        <v>17375156000</v>
+        <v>15850233000</v>
       </c>
       <c r="AY4" t="n">
-        <v>27048652000</v>
+        <v>22098863000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18569403000</v>
+        <v>16533921000</v>
       </c>
       <c r="BA4" t="n">
-        <v>15644954000</v>
+        <v>14383298000</v>
       </c>
       <c r="BB4" t="n">
-        <v>2924449000</v>
+        <v>2150623000</v>
       </c>
       <c r="BC4" t="n">
-        <v>80940595000</v>
+        <v>65994652000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-16467543000</v>
+        <v>-28164606000</v>
       </c>
       <c r="BE4" t="n">
-        <v>97408138000</v>
+        <v>94159258000</v>
       </c>
       <c r="BF4" t="n">
-        <v>12547176000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>95358854000</v>
-      </c>
+        <v>10967852000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>1134916000</v>
+        <v>1034637000</v>
       </c>
       <c r="BI4" t="n">
-        <v>83726046000</v>
+        <v>82156769000</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>839209249000</v>
+        <v>758503915000</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>6298764000</v>
+        <v>4812288000</v>
       </c>
       <c r="BN4" t="n">
-        <v>25940546000</v>
+        <v>17566748000</v>
       </c>
       <c r="BO4" t="n">
-        <v>29368583000</v>
+        <v>28079234000</v>
       </c>
       <c r="BP4" t="n">
-        <v>642026686000</v>
+        <v>577148901000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>990898000</v>
+        <v>567532000</v>
       </c>
       <c r="BR4" t="n">
-        <v>641035788000</v>
+        <v>576581369000</v>
       </c>
       <c r="BS4" t="n">
-        <v>118870904000</v>
+        <v>119032542000</v>
       </c>
       <c r="BT4" t="n">
-        <v>3992793000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>-326640000</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>3992793000</v>
-      </c>
+        <v>4179618000</v>
+      </c>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
       <c r="BW4" t="n">
-        <v>12710973000</v>
+        <v>7684584000</v>
       </c>
       <c r="BX4" t="n">
-        <v>1109845000</v>
+        <v>628210000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11601128000</v>
+        <v>7056374000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>11601128000</v>
+        <v>7056374000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>76325000</v>
+      </c>
       <c r="C5" t="n">
-        <v>4996884000</v>
+        <v>9229924579</v>
       </c>
       <c r="D5" t="n">
-        <v>4996884000</v>
+        <v>9306249579</v>
       </c>
       <c r="E5" t="n">
-        <v>307361145000</v>
+        <v>251937015000</v>
       </c>
       <c r="F5" t="n">
-        <v>322438293000</v>
+        <v>260112738000</v>
       </c>
       <c r="G5" t="n">
-        <v>61567272000</v>
+        <v>25461125000</v>
       </c>
       <c r="H5" t="n">
-        <v>404174475000</v>
+        <v>300188792000</v>
       </c>
       <c r="I5" t="n">
-        <v>-24590099000</v>
+        <v>-53519986000</v>
       </c>
       <c r="J5" t="n">
-        <v>61567272000</v>
+        <v>25461125000</v>
       </c>
       <c r="K5" t="n">
-        <v>733147000</v>
+        <v>445054000</v>
       </c>
       <c r="L5" t="n">
-        <v>82469329000</v>
+        <v>40521108000</v>
       </c>
       <c r="M5" t="n">
-        <v>169027227000</v>
+        <v>114102945000</v>
       </c>
       <c r="N5" t="n">
-        <v>124674246000</v>
+        <v>55146368000</v>
       </c>
       <c r="O5" t="n">
-        <v>42204917000</v>
+        <v>14625260000</v>
       </c>
       <c r="P5" t="n">
-        <v>82469329000</v>
+        <v>40521108000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2408781000</v>
+        <v>2631439000</v>
       </c>
       <c r="R5" t="n">
-        <v>56063172000</v>
+        <v>-6920988000</v>
       </c>
       <c r="S5" t="n">
-        <v>3856592000</v>
+        <v>17547152000</v>
       </c>
       <c r="T5" t="n">
-        <v>429113000</v>
+        <v>817490000</v>
       </c>
       <c r="U5" t="n">
-        <v>429113000</v>
+        <v>817490000</v>
       </c>
       <c r="V5" t="n">
-        <v>1051880642000</v>
+        <v>827736783000</v>
       </c>
       <c r="W5" t="n">
-        <v>113968985000</v>
+        <v>84749731000</v>
       </c>
       <c r="X5" t="n">
-        <v>182008000</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>129906000</v>
+        <v>50124000</v>
       </c>
       <c r="Z5" t="n">
-        <v>26563862000</v>
+        <v>10773159000</v>
       </c>
       <c r="AA5" t="n">
-        <v>87093209000</v>
+        <v>73926448000</v>
       </c>
       <c r="AB5" t="n">
-        <v>535311000</v>
+        <v>344611000</v>
       </c>
       <c r="AC5" t="n">
-        <v>86557898000</v>
+        <v>73581837000</v>
       </c>
       <c r="AD5" t="n">
-        <v>937911657000</v>
+        <v>742987052000</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>235345084000</v>
+        <v>186186290000</v>
       </c>
       <c r="AG5" t="n">
-        <v>197836000</v>
+        <v>100443000</v>
       </c>
       <c r="AH5" t="n">
-        <v>235147248000</v>
+        <v>186085847000</v>
       </c>
       <c r="AI5" t="n">
-        <v>235767000</v>
+        <v>7909066000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>360427217000</v>
+        <v>388253364000</v>
       </c>
       <c r="AK5" t="n">
-        <v>165582243000</v>
+        <v>178265822000</v>
       </c>
       <c r="AL5" t="n">
-        <v>59621473000</v>
+        <v>82833553000</v>
       </c>
       <c r="AM5" t="n">
-        <v>135223501000</v>
+        <v>127153989000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1176554888000</v>
+        <v>882883151000</v>
       </c>
       <c r="AO5" t="n">
-        <v>263233330000</v>
+        <v>193416085000</v>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>3466015000</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>27092067000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>79049000</v>
-      </c>
+        <v>32972177000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>13546259000</v>
+        <v>10068514000</v>
       </c>
       <c r="AU5" t="n">
-        <v>13546259000</v>
+        <v>10068514000</v>
       </c>
       <c r="AV5" t="n">
-        <v>79555170000</v>
+        <v>62848123000</v>
       </c>
       <c r="AW5" t="n">
-        <v>61603834000</v>
+        <v>47334307000</v>
       </c>
       <c r="AX5" t="n">
-        <v>17951336000</v>
+        <v>15513816000</v>
       </c>
       <c r="AY5" t="n">
-        <v>30619994000</v>
+        <v>19237181000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20902057000</v>
+        <v>15059983000</v>
       </c>
       <c r="BA5" t="n">
-        <v>17505441000</v>
+        <v>13380957000</v>
       </c>
       <c r="BB5" t="n">
-        <v>3396616000</v>
+        <v>1679026000</v>
       </c>
       <c r="BC5" t="n">
-        <v>87867815000</v>
+        <v>53183092000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-14490057000</v>
+        <v>-33498942000</v>
       </c>
       <c r="BE5" t="n">
-        <v>102357872000</v>
+        <v>86682034000</v>
       </c>
       <c r="BF5" t="n">
-        <v>12013657000</v>
+        <v>8432856000</v>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>1180278000</v>
+        <v>964236000</v>
       </c>
       <c r="BI5" t="n">
-        <v>89163937000</v>
+        <v>77284942000</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>913321558000</v>
-      </c>
-      <c r="BL5" t="inlineStr"/>
+        <v>689467066000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>15000000</v>
+      </c>
       <c r="BM5" t="n">
-        <v>6439589000</v>
+        <v>4026070000</v>
       </c>
       <c r="BN5" t="n">
-        <v>54858788000</v>
+        <v>12014562000</v>
       </c>
       <c r="BO5" t="n">
-        <v>28891019000</v>
+        <v>24279467000</v>
       </c>
       <c r="BP5" t="n">
-        <v>680591537000</v>
+        <v>516348360000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>835020000</v>
+        <v>541455000</v>
       </c>
       <c r="BR5" t="n">
-        <v>679756517000</v>
+        <v>515806905000</v>
       </c>
       <c r="BS5" t="n">
-        <v>124056061000</v>
+        <v>119764346000</v>
       </c>
       <c r="BT5" t="n">
-        <v>3125119000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>-230150000</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>3355269000</v>
-      </c>
+        <v>4645881000</v>
+      </c>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
       <c r="BW5" t="n">
-        <v>15359445000</v>
+        <v>8373380000</v>
       </c>
       <c r="BX5" t="n">
-        <v>1015444000</v>
+        <v>642711000</v>
       </c>
       <c r="BY5" t="n">
-        <v>14344001000</v>
+        <v>7730669000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14344001000</v>
+        <v>7730669000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>76325000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>12544351572</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12620676572</v>
+      </c>
+      <c r="E6" t="n">
+        <v>182574530000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>188823596000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21583382000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>222421400000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-74455046000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21583382000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>567207000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>34165011000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>68410383000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46843583000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>12678572000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>34165011000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2639741000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-19866098000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>23255998000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1120269000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1120269000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>747835647000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>48785858000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6044836000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>114197000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7925773000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>34701052000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>455680000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>34245372000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>699049789000</v>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>154122544000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>111527000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>154011017000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>11786329000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>383977080000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>193276921000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76590346000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>114109813000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>794679230000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>170084487000</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>31236579000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>9424077000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9424077000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>59877447000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>44467980000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>15409467000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15415175000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>12581629000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11927786000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>653843000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>41510173000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-42767837000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>84278010000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7711177000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>950788000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>75616045000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>624594743000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>3139366000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>6325590000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>20213741000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>461697523000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>433571000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>461263952000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>122246328000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4915503000</v>
+      </c>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="n">
+        <v>6028692000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>346833000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>5681859000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>5681859000</v>
       </c>
     </row>
   </sheetData>
@@ -2567,7 +2724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2829,618 +2986,674 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>5508444000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>-15332332000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9814093000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1092763000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-506596000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7730669000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7056374000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6545000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>667750000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-9115710000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-77380000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-4077204000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>1092763000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>1092763000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-5518239000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-5518239000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-15332332000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>9814093000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3768420000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2055693000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>333151000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21000000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1139608000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5705433000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4565825000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>230710000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1137501000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-906791000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-101653000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>404943000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-506596000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>6015040000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-1614979000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-10124230000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-27967933000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-1231991000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>24124038000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-5048344000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>23190867000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10605000</v>
-      </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>2981520000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>205562000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2775958000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3822652000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2200825000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>-1494246000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-24248878000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>-253584000</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>-7694257000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>-253584000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>169216000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-16645966000</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>16978530000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" t="n">
-        <v>-11589256000</v>
+        <v>-59373537000</v>
       </c>
       <c r="E3" t="n">
-        <v>24778262000</v>
+        <v>29966892000</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3662176000</v>
       </c>
       <c r="G3" t="n">
-        <v>-860244000</v>
+        <v>-3759417000</v>
       </c>
       <c r="H3" t="n">
-        <v>7056374000</v>
+        <v>11601128000</v>
       </c>
       <c r="I3" t="n">
-        <v>11601128000</v>
+        <v>14344001000</v>
       </c>
       <c r="J3" t="n">
-        <v>21450000</v>
+        <v>65462000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4566204000</v>
+        <v>-2808335000</v>
       </c>
       <c r="L3" t="n">
-        <v>5775062000</v>
+        <v>-29111730000</v>
       </c>
       <c r="M3" t="n">
-        <v>-661090000</v>
+        <v>12249155000</v>
       </c>
       <c r="N3" t="n">
-        <v>-5837587000</v>
+        <v>-14806704000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
+        <v>3662176000</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3662176000</v>
       </c>
       <c r="S3" t="n">
-        <v>13189006000</v>
+        <v>-29406645000</v>
       </c>
       <c r="T3" t="n">
-        <v>13189006000</v>
+        <v>-29406645000</v>
       </c>
       <c r="U3" t="n">
-        <v>-11589256000</v>
+        <v>-59373537000</v>
       </c>
       <c r="V3" t="n">
-        <v>24778262000</v>
+        <v>29966892000</v>
       </c>
       <c r="W3" t="n">
-        <v>5444456000</v>
+        <v>5565448000</v>
       </c>
       <c r="X3" t="n">
-        <v>2652582000</v>
+        <v>15789000</v>
       </c>
       <c r="Y3" t="n">
-        <v>294406000</v>
+        <v>605708000</v>
       </c>
       <c r="Z3" t="n">
-        <v>187239000</v>
+        <v>258555000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1237578000</v>
+        <v>298620000</v>
       </c>
       <c r="AB3" t="n">
-        <v>3638578000</v>
+        <v>3286682000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2401000000</v>
+        <v>-2988062000</v>
       </c>
       <c r="AD3" t="n">
-        <v>466156000</v>
+        <v>959090000</v>
       </c>
       <c r="AE3" t="n">
-        <v>498656000</v>
+        <v>2204020000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-32500000</v>
+        <v>-1244930000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-463954000</v>
+        <v>-3246704000</v>
       </c>
       <c r="AH3" t="n">
-        <v>396290000</v>
+        <v>512713000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-860244000</v>
+        <v>-3759417000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-15785722000</v>
+        <v>20737947000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-1415679000</v>
+        <v>-940418000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-26912880000</v>
+        <v>11931000000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-125247517000</v>
+        <v>-7135118000</v>
       </c>
       <c r="AN3" t="n">
-        <v>26526859000</v>
+        <v>-3486083000</v>
       </c>
       <c r="AO3" t="n">
-        <v>69728451000</v>
+        <v>20179422000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2079327000</v>
+        <v>2372779000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-4026623000</v>
+        <v>29093476000</v>
       </c>
       <c r="AR3" t="n">
-        <v>38467000</v>
+        <v>173586000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2314810000</v>
+        <v>913731000</v>
       </c>
       <c r="AT3" t="n">
-        <v>3584039000</v>
+        <v>3189150000</v>
       </c>
       <c r="AU3" t="n">
-        <v>209114000</v>
+        <v>254898000</v>
       </c>
       <c r="AV3" t="n">
-        <v>3374925000</v>
+        <v>2934252000</v>
       </c>
       <c r="AW3" t="n">
-        <v>4050072000</v>
+        <v>399426000</v>
       </c>
       <c r="AX3" t="n">
-        <v>929341000</v>
+        <v>861371000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1055589000</v>
+        <v>7123397000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-5133920000</v>
+        <v>-31303603000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>16978530000</v>
-      </c>
-      <c r="C4" t="n">
+        <v>-16645966000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>-11589256000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24778262000</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>-59373537000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>29966892000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3662176000</v>
-      </c>
       <c r="G4" t="n">
-        <v>-3759417000</v>
+        <v>-860244000</v>
       </c>
       <c r="H4" t="n">
+        <v>7056374000</v>
+      </c>
+      <c r="I4" t="n">
         <v>11601128000</v>
       </c>
-      <c r="I4" t="n">
-        <v>14344001000</v>
-      </c>
       <c r="J4" t="n">
-        <v>65462000</v>
+        <v>21450000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2808335000</v>
+        <v>-4566204000</v>
       </c>
       <c r="L4" t="n">
-        <v>-29111730000</v>
+        <v>5775062000</v>
       </c>
       <c r="M4" t="n">
-        <v>12249155000</v>
+        <v>-661090000</v>
       </c>
       <c r="N4" t="n">
-        <v>-14806704000</v>
+        <v>-5837587000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>3662176000</v>
-      </c>
-      <c r="Q4" t="n">
         <v>0</v>
       </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>3662176000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-29406645000</v>
+        <v>13189006000</v>
       </c>
       <c r="T4" t="n">
-        <v>-29406645000</v>
+        <v>13189006000</v>
       </c>
       <c r="U4" t="n">
-        <v>-59373537000</v>
+        <v>-11589256000</v>
       </c>
       <c r="V4" t="n">
-        <v>29966892000</v>
+        <v>24778262000</v>
       </c>
       <c r="W4" t="n">
-        <v>5565448000</v>
+        <v>5444456000</v>
       </c>
       <c r="X4" t="n">
-        <v>15789000</v>
+        <v>2652582000</v>
       </c>
       <c r="Y4" t="n">
-        <v>605708000</v>
+        <v>294406000</v>
       </c>
       <c r="Z4" t="n">
-        <v>258555000</v>
+        <v>187239000</v>
       </c>
       <c r="AA4" t="n">
-        <v>298620000</v>
+        <v>1237578000</v>
       </c>
       <c r="AB4" t="n">
-        <v>3286682000</v>
+        <v>3638578000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2988062000</v>
+        <v>-2401000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>959090000</v>
+        <v>466156000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2204020000</v>
+        <v>498656000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1244930000</v>
+        <v>-32500000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3246704000</v>
+        <v>-463954000</v>
       </c>
       <c r="AH4" t="n">
-        <v>512713000</v>
+        <v>396290000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3759417000</v>
+        <v>-860244000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20737947000</v>
+        <v>-15785722000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-940418000</v>
+        <v>-1415679000</v>
       </c>
       <c r="AL4" t="n">
-        <v>11931000000</v>
+        <v>-26912880000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-7135118000</v>
+        <v>-125247517000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-3486083000</v>
+        <v>26526859000</v>
       </c>
       <c r="AO4" t="n">
-        <v>20179422000</v>
+        <v>69728451000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2372779000</v>
+        <v>2079327000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29093476000</v>
+        <v>-4026623000</v>
       </c>
       <c r="AR4" t="n">
-        <v>173586000</v>
+        <v>38467000</v>
       </c>
       <c r="AS4" t="n">
-        <v>913731000</v>
+        <v>2314810000</v>
       </c>
       <c r="AT4" t="n">
-        <v>3189150000</v>
+        <v>3584039000</v>
       </c>
       <c r="AU4" t="n">
-        <v>254898000</v>
+        <v>209114000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2934252000</v>
+        <v>3374925000</v>
       </c>
       <c r="AW4" t="n">
-        <v>399426000</v>
+        <v>4050072000</v>
       </c>
       <c r="AX4" t="n">
-        <v>861371000</v>
+        <v>929341000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7123397000</v>
+        <v>1055589000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-31303603000</v>
+        <v>-5133920000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-51205580000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-253584000</v>
-      </c>
+        <v>5508444000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>-209286625000</v>
+        <v>-15332332000</v>
       </c>
       <c r="E5" t="n">
-        <v>237490515000</v>
+        <v>9814093000</v>
       </c>
       <c r="F5" t="n">
-        <v>4189286000</v>
+        <v>1092763000</v>
       </c>
       <c r="G5" t="n">
-        <v>-11154975000</v>
+        <v>-506596000</v>
       </c>
       <c r="H5" t="n">
-        <v>14344001000</v>
+        <v>7730669000</v>
       </c>
       <c r="I5" t="n">
-        <v>98710644000</v>
+        <v>7056374000</v>
       </c>
       <c r="J5" t="n">
-        <v>2325000</v>
+        <v>6545000</v>
       </c>
       <c r="K5" t="n">
-        <v>-84368968000</v>
+        <v>667750000</v>
       </c>
       <c r="L5" t="n">
-        <v>-11452459000</v>
+        <v>-9115710000</v>
       </c>
       <c r="M5" t="n">
-        <v>-898790000</v>
+        <v>-77380000</v>
       </c>
       <c r="N5" t="n">
-        <v>-29737649000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-7694257000</v>
-      </c>
+        <v>-4077204000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>3935702000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-253584000</v>
-      </c>
+        <v>1092763000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>4189286000</v>
+        <v>1092763000</v>
       </c>
       <c r="S5" t="n">
-        <v>28203890000</v>
+        <v>-5518239000</v>
       </c>
       <c r="T5" t="n">
-        <v>28203890000</v>
+        <v>-5518239000</v>
       </c>
       <c r="U5" t="n">
-        <v>-209286625000</v>
+        <v>-15332332000</v>
       </c>
       <c r="V5" t="n">
-        <v>237490515000</v>
+        <v>9814093000</v>
       </c>
       <c r="W5" t="n">
-        <v>-32865904000</v>
+        <v>3768420000</v>
       </c>
       <c r="X5" t="n">
-        <v>168087000</v>
+        <v>2055693000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1404258000</v>
+        <v>333151000</v>
       </c>
       <c r="Z5" t="n">
-        <v>175290000</v>
+        <v>21000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>5678546000</v>
+        <v>1139608000</v>
       </c>
       <c r="AB5" t="n">
-        <v>11450869000</v>
+        <v>5705433000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-5772323000</v>
+        <v>-4565825000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-16522979000</v>
+        <v>230710000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1005597000</v>
+        <v>1137501000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-17528576000</v>
+        <v>-906791000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-10712545000</v>
+        <v>-101653000</v>
       </c>
       <c r="AH5" t="n">
-        <v>442430000</v>
+        <v>404943000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-11154975000</v>
+        <v>-506596000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-40050605000</v>
+        <v>6015040000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-13952874000</v>
+        <v>-1614979000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-39138837000</v>
+        <v>-10124230000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-48821288000</v>
+        <v>-27967933000</v>
       </c>
       <c r="AN5" t="n">
-        <v>18453712000</v>
+        <v>-1231991000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-11517153000</v>
+        <v>24124038000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2745892000</v>
+        <v>-5048344000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>24783190000</v>
+        <v>23190867000</v>
       </c>
       <c r="AR5" t="n">
-        <v>499203000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>169216000</v>
-      </c>
+        <v>10605000</v>
+      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>3781902000</v>
+        <v>2981520000</v>
       </c>
       <c r="AU5" t="n">
-        <v>192574000</v>
+        <v>205562000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3589328000</v>
+        <v>2775958000</v>
       </c>
       <c r="AW5" t="n">
-        <v>8176760000</v>
+        <v>3822652000</v>
       </c>
       <c r="AX5" t="n">
-        <v>307867000</v>
+        <v>2200825000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1205553000</v>
+        <v>-1494246000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-43673581000</v>
+        <v>-24248878000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2521063000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>-9061902000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4459956000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-214461000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5681859000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>7730669000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-5328000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-2043482000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-6956692000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-9422000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-2022928000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-4601946000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-4601946000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-9061902000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4459956000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2177686000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1146361000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>40304000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6184000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>409958000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6241898000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-5831940000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>669727000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>672977000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-3250000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-132518000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>81943000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-214461000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2735524000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-1354629000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-6866774000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-15494332000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-8289182000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>15118065000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1798675000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-3869526000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>8302000</v>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>3398612000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>215920000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3182692000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4390883000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1136212000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8269366000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-13698672000</v>
       </c>
     </row>
   </sheetData>
@@ -4050,202 +4263,202 @@
       </c>
       <c r="DO1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="DT1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="FC1" t="inlineStr">
@@ -4335,7 +4548,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Hongbin  Sun', 'age': 62, 'title': 'Founder &amp; Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 139013, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mengde  Wang', 'age': 53, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 272234, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shuping  Huang', 'age': 44, 'title': 'Executive President, President of the South China Regional Group &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 1241849, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Zhixia  Ma', 'age': 52, 'title': 'Executive President, COO, GM of the Real Estate Operation Centre &amp; Executive Director', 'yearBorn': 1973, 'fiscalYear': 2025, 'totalPay': 1291662, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zheyi  Sun', 'age': 35, 'title': 'VP, President of Beijing Regional Branch &amp; Executive Director', 'yearBorn': 1990, 'fiscalYear': 2025, 'totalPay': 1270810, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liu  Wensheng', 'title': 'Investor Relations Director', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Hongbin  Sun', 'age': 62, 'title': 'Founder &amp; Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 138902, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Shuping  Huang', 'age': 44, 'title': 'Executive President, President of the South China Regional Group &amp; Executive Director', 'yearBorn': 1981, 'fiscalYear': 2025, 'totalPay': 1240859, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Zhixia  Ma', 'age': 52, 'title': 'Executive President, COO, GM of the Real Estate Operation Centre &amp; Executive Director', 'yearBorn': 1973, 'fiscalYear': 2025, 'totalPay': 1290633, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Zheyi  Sun', 'age': 35, 'title': 'VP, President of Beijing Regional Branch &amp; Executive Director', 'yearBorn': 1990, 'fiscalYear': 2025, 'totalPay': 1269797, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Liu  Wensheng', 'title': 'Investor Relations Director', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4354,7 +4567,7 @@
         <v>10</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -4371,28 +4584,28 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.92</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AJ2" t="n">
         <v>1628640000</v>
@@ -4404,31 +4617,31 @@
         <v>2.76</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.356</v>
+        <v>0.338</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1.3301451</v>
+        <v>-1.0415359</v>
       </c>
       <c r="AO2" t="n">
-        <v>37454000</v>
+        <v>227248694</v>
       </c>
       <c r="AP2" t="n">
-        <v>37454000</v>
+        <v>227248694</v>
       </c>
       <c r="AQ2" t="n">
-        <v>173896731</v>
+        <v>160910179</v>
       </c>
       <c r="AR2" t="n">
-        <v>207790982</v>
+        <v>133401038</v>
       </c>
       <c r="AS2" t="n">
-        <v>207790982</v>
+        <v>133401038</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.93</v>
+        <v>0.72</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4437,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>14827257856</v>
+        <v>11603941376</v>
       </c>
       <c r="AY2" t="n">
-        <v>14988423110</v>
+        <v>11603940472</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BA2" t="n">
         <v>1.92</v>
@@ -4452,16 +4665,16 @@
         <v>48.91011</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.87</v>
+        <v>0.72</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.32864368</v>
+        <v>0.2571994</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.0562</v>
+        <v>1.0014</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.2916</v>
+        <v>1.2486</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -4478,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>207210708992</v>
+        <v>204560367616</v>
       </c>
       <c r="BL2" t="n">
         <v>-0.27327</v>
@@ -4490,19 +4703,19 @@
         <v>16116583990</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.25895</v>
+        <v>0.25316998</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.11931</v>
+        <v>0.118760005</v>
       </c>
       <c r="BQ2" t="n">
         <v>16116583990</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.1350899</v>
+        <v>3.1334262</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.29345253</v>
+        <v>0.22978044</v>
       </c>
       <c r="BT2" t="n">
         <v>1767139200</v>
@@ -4520,22 +4733,22 @@
         <v>-1.32</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.69165385</v>
+        <v>-0.6912868</v>
       </c>
       <c r="BZ2" t="n">
         <v>0.43</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.593</v>
+        <v>4.534</v>
       </c>
       <c r="CB2" t="n">
-        <v>7.492</v>
+        <v>7.397</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.32608694</v>
+        <v>-0.5</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="CE2" t="n">
         <v>2</v>
@@ -4549,19 +4762,19 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>0.92</v>
+        <v>0.72</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.6055912</v>
+        <v>1.6043429</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.8137928</v>
+        <v>0.8131601000000001</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.1660852</v>
+        <v>1.1651785</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.0788832</v>
+        <v>1.0780444</v>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
@@ -4665,147 +4878,147 @@
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-1.0752678</v>
+          <t>SUNAC</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Sunac China Holdings Limited</t>
+        </is>
       </c>
       <c r="DQ2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>SUNAC</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.72</v>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>Sunac China Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DT2" t="b">
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>finmb_29545876</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EB2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EC2" t="n">
+        <v>-1.1345551</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.28139997</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.28100654</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.5286</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.42335415</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="n">
         <v>1286415000000</v>
       </c>
-      <c r="DV2" t="n">
-        <v>-0.00999999</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>0.92 - 0.94</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1780453614</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_29545876</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
+      <c r="EM2" t="n">
         <v>0</v>
       </c>
-      <c r="EG2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>0.69 - 0.74</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="EH2" t="n">
-        <v>173896731</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.050000012</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.05747128</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>0.87 - 1.92</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.99999994</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.5208333000000001</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-32.608692</v>
-      </c>
-      <c r="EO2" t="n">
+      <c r="EP2" t="n">
+        <v>160910179</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>0.030000031</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>0.043478306</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>0.69 - 1.92</t>
+        </is>
+      </c>
+      <c r="ET2" t="n">
+        <v>-1.1999999</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>-0.625</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-50</v>
+      </c>
+      <c r="EW2" t="n">
         <v>1756292340</v>
       </c>
-      <c r="EP2" t="n">
+      <c r="EX2" t="n">
         <v>1756728000</v>
       </c>
-      <c r="EQ2" t="b">
+      <c r="EY2" t="b">
         <v>1</v>
       </c>
-      <c r="ER2" t="n">
+      <c r="EZ2" t="n">
         <v>-1.32</v>
       </c>
-      <c r="ES2" t="n">
-        <v>-0.69165385</v>
-      </c>
-      <c r="ET2" t="n">
+      <c r="FA2" t="n">
+        <v>-0.6912868</v>
+      </c>
+      <c r="FB2" t="n">
         <v>-0.63461</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-1.4497093</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.13620001</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-0.12895286</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>-0.37159997</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>-0.28770515</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FB2" t="b">
-        <v>0</v>
       </c>
       <c r="FC2" t="inlineStr"/>
     </row>
